--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-researchstudy.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-researchstudy.xlsx
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>ObservationalStudyProtocolVersion; Study;
@@ -324,16 +324,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -370,7 +370,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -390,16 +390,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ResearchStudy.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子</t>
-  </si>
-  <si>
-    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
   </si>
   <si>
     <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
@@ -419,7 +419,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースのバージョンが最後に変更されたとき」</t>
+    <t>リソースのバージョンが最後に変更されたとき</t>
   </si>
   <si>
     <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
@@ -444,8 +444,8 @@
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
   </si>
   <si>
-    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
-この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
   </si>
   <si>
     <t>Meta.source</t>
@@ -513,7 +513,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/common-tags</t>
@@ -632,7 +632,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -660,10 +660,10 @@
 </t>
   </si>
   <si>
-    <t>研究のためのビジネス識別子 / Business Identifier for study</t>
-  </si>
-  <si>
-    <t>スポンサーまたは他のシステムによるこの調査研究に割り当てられた識別子。 / Identifiers assigned to this research study by the sponsor or other systems.</t>
+    <t>研究のためのビジネスidentifier / Business Identifier for study</t>
+  </si>
+  <si>
+    <t>スポンサーまたは他のシステムによるこの調査研究に割り当てられたidentifier。 / Identifiers assigned to this research study by the sponsor or other systems.</t>
   </si>
   <si>
     <t>さまざまな参加システムで知られており、サーバー全体で一貫性を保っている方法で、調査研究を特定できます。 / Allows identification of the research study as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -703,7 +703,7 @@
 </t>
   </si>
   <si>
-    <t>研究の実行に従った手順 / Steps followed in executing study</t>
+    <t>研究の実行に従ったプロシジャー（処置等） / Steps followed in executing study</t>
   </si>
   <si>
     <t>一連のステップは、研究の実行の一部として実行されると予想されます。 / The set of steps expected to be performed as part of the execution of the study.</t>
